--- a/2026 1-15 Apr Number.xlsx
+++ b/2026 1-15 Apr Number.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DA7F097-C081-42A7-84F5-BA97AA13EFFD}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B9B069F-C215-4B78-BF57-94381800BEA0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
@@ -111,6 +111,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -430,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D1233"/>
+  <dimension ref="A1:D1469"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
@@ -17692,7 +17696,7 @@
         <v>46133.291666666664</v>
       </c>
       <c r="B1233" s="4">
-        <v>32.567261845724929</v>
+        <v>32.568750031789143</v>
       </c>
       <c r="C1233" s="4">
         <v>38.914638913279838</v>
@@ -17700,6 +17704,3278 @@
       <c r="D1233" s="4">
         <v>38.788238579915713</v>
       </c>
+    </row>
+    <row r="1234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1234" s="1">
+        <v>46133.333333333336</v>
+      </c>
+      <c r="B1234" s="4">
+        <v>32.548958905537923</v>
+      </c>
+      <c r="C1234" s="4">
+        <v>38.930929319786301</v>
+      </c>
+      <c r="D1234" s="4">
+        <v>38.827561889706054</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1235" s="1">
+        <v>46133.375</v>
+      </c>
+      <c r="B1235" s="4">
+        <v>32.547708638509114</v>
+      </c>
+      <c r="C1235" s="4">
+        <v>38.930334568023682</v>
+      </c>
+      <c r="D1235" s="4">
+        <v>38.859994174534528</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1236" s="1">
+        <v>46133.416666666664</v>
+      </c>
+      <c r="B1236" s="4">
+        <v>32.600937747955321</v>
+      </c>
+      <c r="C1236" s="4">
+        <v>39.036666997273763</v>
+      </c>
+      <c r="D1236" s="4">
+        <v>38.949557088011353</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1237" s="1">
+        <v>46133.458333333336</v>
+      </c>
+      <c r="B1237" s="4">
+        <v>32.697187487284346</v>
+      </c>
+      <c r="C1237" s="4">
+        <v>39.156090309506375</v>
+      </c>
+      <c r="D1237" s="4">
+        <v>39.04172382624634</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1238" s="1">
+        <v>46133.5</v>
+      </c>
+      <c r="B1238" s="4">
+        <v>32.803334172566728</v>
+      </c>
+      <c r="C1238" s="4">
+        <v>39.286566525413882</v>
+      </c>
+      <c r="D1238" s="4">
+        <v>39.1602105698869</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1239" s="1">
+        <v>46133.541666666664</v>
+      </c>
+      <c r="B1239" s="4">
+        <v>32.84645783106486</v>
+      </c>
+      <c r="C1239" s="4">
+        <v>39.2937844382392</v>
+      </c>
+      <c r="D1239" s="4">
+        <v>39.201067466231585</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1240" s="1">
+        <v>46133.583333333336</v>
+      </c>
+      <c r="B1240" s="4">
+        <v>32.849809779061211</v>
+      </c>
+      <c r="C1240" s="4">
+        <v>39.277204884423149</v>
+      </c>
+      <c r="D1240" s="4">
+        <v>39.164554457254312</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1241" s="1">
+        <v>46133.625</v>
+      </c>
+      <c r="B1241" s="4">
+        <v>32.849983210033841</v>
+      </c>
+      <c r="C1241" s="4">
+        <v>39.272517066531712</v>
+      </c>
+      <c r="D1241" s="4">
+        <v>39.125085898837817</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1242" s="1">
+        <v>46133.666666666664</v>
+      </c>
+      <c r="B1242" s="4">
+        <v>32.832245263745712</v>
+      </c>
+      <c r="C1242" s="4">
+        <v>39.214746078915063</v>
+      </c>
+      <c r="D1242" s="4">
+        <v>39.115067293021362</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1243" s="1">
+        <v>46133.708333333336</v>
+      </c>
+      <c r="B1243" s="4">
+        <v>32.784700946055857</v>
+      </c>
+      <c r="C1243" s="4">
+        <v>39.102470135512178</v>
+      </c>
+      <c r="D1243" s="4">
+        <v>38.981809583447642</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1244" s="1">
+        <v>46133.75</v>
+      </c>
+      <c r="B1244" s="4">
+        <v>32.716987076070573</v>
+      </c>
+      <c r="C1244" s="4">
+        <v>39.035542956104983</v>
+      </c>
+      <c r="D1244" s="4">
+        <v>38.915394078038474</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1245" s="1">
+        <v>46133.791666666664</v>
+      </c>
+      <c r="B1245" s="4">
+        <v>32.667798796983867</v>
+      </c>
+      <c r="C1245" s="4">
+        <v>38.956111356947154</v>
+      </c>
+      <c r="D1245" s="4">
+        <v>38.824519352424382</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1246" s="1">
+        <v>46133.833333333336</v>
+      </c>
+      <c r="B1246" s="4">
+        <v>32.601109805918519</v>
+      </c>
+      <c r="C1246" s="4">
+        <v>38.851850164504278</v>
+      </c>
+      <c r="D1246" s="4">
+        <v>38.714222247676936</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1247" s="1">
+        <v>46133.875</v>
+      </c>
+      <c r="B1247" s="4">
+        <v>32.566117347370493</v>
+      </c>
+      <c r="C1247" s="4">
+        <v>38.789257082106573</v>
+      </c>
+      <c r="D1247" s="4">
+        <v>38.640537830696431</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1248" s="1">
+        <v>46133.916666666664</v>
+      </c>
+      <c r="B1248" s="4">
+        <v>32.522082869211836</v>
+      </c>
+      <c r="C1248" s="4">
+        <v>38.777181501388547</v>
+      </c>
+      <c r="D1248" s="4">
+        <v>38.642995331549415</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1249" s="1">
+        <v>46133.958333333336</v>
+      </c>
+      <c r="B1249" s="4">
+        <v>32.532593327981452</v>
+      </c>
+      <c r="C1249" s="4">
+        <v>38.761104214986169</v>
+      </c>
+      <c r="D1249" s="4">
+        <v>38.595589466520501</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1250" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B1250" s="4">
+        <v>32.530037051218528</v>
+      </c>
+      <c r="C1250" s="4">
+        <v>38.772100236680771</v>
+      </c>
+      <c r="D1250" s="4">
+        <v>38.597182772010292</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1251" s="1">
+        <v>46134.041666666664</v>
+      </c>
+      <c r="B1251" s="4">
+        <v>32.500521083672844</v>
+      </c>
+      <c r="C1251" s="4">
+        <v>38.753819137149385</v>
+      </c>
+      <c r="D1251" s="4">
+        <v>38.586553969243866</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1252" s="1">
+        <v>46134.083333333336</v>
+      </c>
+      <c r="B1252" s="4">
+        <v>32.45666268197899</v>
+      </c>
+      <c r="C1252" s="4">
+        <v>38.691538060506183</v>
+      </c>
+      <c r="D1252" s="4">
+        <v>38.563189999585909</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1253" s="1">
+        <v>46134.125</v>
+      </c>
+      <c r="B1253" s="4">
+        <v>32.416027112455446</v>
+      </c>
+      <c r="C1253" s="4">
+        <v>38.663273913671098</v>
+      </c>
+      <c r="D1253" s="4">
+        <v>38.553653234242105</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1254" s="1">
+        <v>46134.166666666664</v>
+      </c>
+      <c r="B1254" s="4">
+        <v>32.43436811870999</v>
+      </c>
+      <c r="C1254" s="4">
+        <v>38.681474436653986</v>
+      </c>
+      <c r="D1254" s="4">
+        <v>38.545898459832564</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1255" s="1">
+        <v>46134.208333333336</v>
+      </c>
+      <c r="B1255" s="4">
+        <v>32.429999902513295</v>
+      </c>
+      <c r="C1255" s="4">
+        <v>38.709583984670189</v>
+      </c>
+      <c r="D1255" s="4">
+        <v>38.569932721842711</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1256" s="1">
+        <v>46134.25</v>
+      </c>
+      <c r="B1256" s="4">
+        <v>32.418125014834935</v>
+      </c>
+      <c r="C1256" s="4">
+        <v>38.713004302183784</v>
+      </c>
+      <c r="D1256" s="4">
+        <v>38.578077050895203</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1257" s="1">
+        <v>46134.291666666664</v>
+      </c>
+      <c r="B1257" s="4">
+        <v>32.406002835874204</v>
+      </c>
+      <c r="C1257" s="4">
+        <v>38.734041461944578</v>
+      </c>
+      <c r="D1257" s="4">
+        <v>38.594423985179674</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1258" s="1">
+        <v>46134.333333333336</v>
+      </c>
+      <c r="B1258" s="4">
+        <v>32.412816512143166</v>
+      </c>
+      <c r="C1258" s="4">
+        <v>38.761082423283504</v>
+      </c>
+      <c r="D1258" s="4">
+        <v>38.654329171323369</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1259" s="1">
+        <v>46134.375</v>
+      </c>
+      <c r="B1259" s="4">
+        <v>32.47127041362581</v>
+      </c>
+      <c r="C1259" s="4">
+        <v>38.837021144475699</v>
+      </c>
+      <c r="D1259" s="4">
+        <v>38.723120521198346</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1260" s="1">
+        <v>46134.416666666664</v>
+      </c>
+      <c r="B1260" s="4">
+        <v>32.561743937901085</v>
+      </c>
+      <c r="C1260" s="4">
+        <v>38.976142393483059</v>
+      </c>
+      <c r="D1260" s="4">
+        <v>38.846297638127567</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1261" s="1">
+        <v>46134.458333333336</v>
+      </c>
+      <c r="B1261" s="4">
+        <v>32.647315713034736</v>
+      </c>
+      <c r="C1261" s="4">
+        <v>39.097398208247292</v>
+      </c>
+      <c r="D1261" s="4">
+        <v>39.010034218695786</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1262" s="1">
+        <v>46134.5</v>
+      </c>
+      <c r="B1262" s="4">
+        <v>32.743767711851334</v>
+      </c>
+      <c r="C1262" s="4">
+        <v>39.227628976223514</v>
+      </c>
+      <c r="D1262" s="4">
+        <v>39.109386189665734</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1263" s="1">
+        <v>46134.541666666664</v>
+      </c>
+      <c r="B1263" s="4">
+        <v>32.838358728090924</v>
+      </c>
+      <c r="C1263" s="4">
+        <v>39.331840911192053</v>
+      </c>
+      <c r="D1263" s="4">
+        <v>39.199568103573029</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1264" s="1">
+        <v>46134.583333333336</v>
+      </c>
+      <c r="B1264" s="4">
+        <v>32.870136659233658</v>
+      </c>
+      <c r="C1264" s="4">
+        <v>39.354374523162839</v>
+      </c>
+      <c r="D1264" s="4">
+        <v>39.243588009930434</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1265" s="1">
+        <v>46134.625</v>
+      </c>
+      <c r="B1265" s="4">
+        <v>32.891296298415568</v>
+      </c>
+      <c r="C1265" s="4">
+        <v>39.3624640765943</v>
+      </c>
+      <c r="D1265" s="4">
+        <v>39.252948103547311</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1266" s="1">
+        <v>46134.666666666664</v>
+      </c>
+      <c r="B1266" s="4">
+        <v>32.869895760218306</v>
+      </c>
+      <c r="C1266" s="4">
+        <v>39.292736101600966</v>
+      </c>
+      <c r="D1266" s="4">
+        <v>39.206876695786924</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1267" s="1">
+        <v>46134.708333333336</v>
+      </c>
+      <c r="B1267" s="4">
+        <v>32.832188272476195</v>
+      </c>
+      <c r="C1267" s="4">
+        <v>39.221945665310592</v>
+      </c>
+      <c r="D1267" s="4">
+        <v>39.143049794501728</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1268" s="1">
+        <v>46134.75</v>
+      </c>
+      <c r="B1268" s="4">
+        <v>32.779688803354901</v>
+      </c>
+      <c r="C1268" s="4">
+        <v>39.139931983947754</v>
+      </c>
+      <c r="D1268" s="4">
+        <v>39.059404726590969</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1269" s="1">
+        <v>46134.791666666664</v>
+      </c>
+      <c r="B1269" s="4">
+        <v>32.703967709695135</v>
+      </c>
+      <c r="C1269" s="4">
+        <v>39.037400035858155</v>
+      </c>
+      <c r="D1269" s="4">
+        <v>38.948224586679281</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1270" s="1">
+        <v>46134.833333333336</v>
+      </c>
+      <c r="B1270" s="4">
+        <v>32.637177901114185</v>
+      </c>
+      <c r="C1270" s="4">
+        <v>38.934218680063886</v>
+      </c>
+      <c r="D1270" s="4">
+        <v>38.81154739308721</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1271" s="1">
+        <v>46134.875</v>
+      </c>
+      <c r="B1271" s="4">
+        <v>32.59476296545445</v>
+      </c>
+      <c r="C1271" s="4">
+        <v>38.859687455495198</v>
+      </c>
+      <c r="D1271" s="4">
+        <v>38.743806544703709</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1272" s="1">
+        <v>46134.916666666664</v>
+      </c>
+      <c r="B1272" s="4">
+        <v>32.547111792948051</v>
+      </c>
+      <c r="C1272" s="4">
+        <v>38.796151417273059</v>
+      </c>
+      <c r="D1272" s="4">
+        <v>38.686015234098143</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1273" s="1">
+        <v>46134.958333333336</v>
+      </c>
+      <c r="B1273" s="4">
+        <v>32.503958098093669</v>
+      </c>
+      <c r="C1273" s="4">
+        <v>38.752007024532311</v>
+      </c>
+      <c r="D1273" s="4">
+        <v>38.63627991900119</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1274" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B1274" s="4">
+        <v>32.455625216166176</v>
+      </c>
+      <c r="C1274" s="4">
+        <v>38.715148398455455</v>
+      </c>
+      <c r="D1274" s="4">
+        <v>38.583257151541858</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1275" s="1">
+        <v>46135.041666666664</v>
+      </c>
+      <c r="B1275" s="4">
+        <v>32.456270506117079</v>
+      </c>
+      <c r="C1275" s="4">
+        <v>38.699921607971191</v>
+      </c>
+      <c r="D1275" s="4">
+        <v>38.55637000186546</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1276" s="1">
+        <v>46135.083333333336</v>
+      </c>
+      <c r="B1276" s="4">
+        <v>32.412083763546413</v>
+      </c>
+      <c r="C1276" s="4">
+        <v>38.649876688040933</v>
+      </c>
+      <c r="D1276" s="4">
+        <v>38.531495815884789</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1277" s="1">
+        <v>46135.125</v>
+      </c>
+      <c r="B1277" s="4">
+        <v>32.410094719548383</v>
+      </c>
+      <c r="C1277" s="4">
+        <v>38.654068960934922</v>
+      </c>
+      <c r="D1277" s="4">
+        <v>38.499119993817928</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1278" s="1">
+        <v>46135.166666666664</v>
+      </c>
+      <c r="B1278" s="4">
+        <v>32.461086339335289</v>
+      </c>
+      <c r="C1278" s="4">
+        <v>38.720324345124077</v>
+      </c>
+      <c r="D1278" s="4">
+        <v>38.533642255568822</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1279" s="1">
+        <v>46135.208333333336</v>
+      </c>
+      <c r="B1279" s="4">
+        <v>32.553819576899208</v>
+      </c>
+      <c r="C1279" s="4">
+        <v>38.81164918475681</v>
+      </c>
+      <c r="D1279" s="4">
+        <v>38.646116019355006</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1280" s="1">
+        <v>46135.25</v>
+      </c>
+      <c r="B1280" s="4">
+        <v>32.600191563500296</v>
+      </c>
+      <c r="C1280" s="4">
+        <v>38.864388082292344</v>
+      </c>
+      <c r="D1280" s="4">
+        <v>38.707364015895891</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1281" s="1">
+        <v>46135.291666666664</v>
+      </c>
+      <c r="B1281" s="4">
+        <v>32.496527671813965</v>
+      </c>
+      <c r="C1281" s="4">
+        <v>38.798489718967012</v>
+      </c>
+      <c r="D1281" s="4">
+        <v>38.674153508351921</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1282" s="1">
+        <v>46135.333333333336</v>
+      </c>
+      <c r="B1282" s="4">
+        <v>32.436875438690187</v>
+      </c>
+      <c r="C1282" s="4">
+        <v>38.789783766330821</v>
+      </c>
+      <c r="D1282" s="4">
+        <v>38.624535031296439</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1283" s="1">
+        <v>46135.375</v>
+      </c>
+      <c r="B1283" s="4">
+        <v>32.447069373660618</v>
+      </c>
+      <c r="C1283" s="4">
+        <v>38.833518909552154</v>
+      </c>
+      <c r="D1283" s="4">
+        <v>38.828863539212662</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1284" s="1">
+        <v>46135.416666666664</v>
+      </c>
+      <c r="B1284" s="4">
+        <v>32.427097263336179</v>
+      </c>
+      <c r="C1284" s="4">
+        <v>38.840358077457971</v>
+      </c>
+      <c r="D1284" s="4">
+        <v>38.847147413207566</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1285" s="1">
+        <v>46135.458333333336</v>
+      </c>
+      <c r="B1285" s="4">
+        <v>32.49745129532284</v>
+      </c>
+      <c r="C1285" s="4">
+        <v>38.928475311824258</v>
+      </c>
+      <c r="D1285" s="4">
+        <v>38.836452738710562</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1286" s="1">
+        <v>46135.5</v>
+      </c>
+      <c r="B1286" s="4">
+        <v>32.588574243846693</v>
+      </c>
+      <c r="C1286" s="4">
+        <v>39.050773578219946</v>
+      </c>
+      <c r="D1286" s="4">
+        <v>38.951539347057412</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1287" s="1">
+        <v>46135.541666666664</v>
+      </c>
+      <c r="B1287" s="4">
+        <v>32.646009404199162</v>
+      </c>
+      <c r="C1287" s="4">
+        <v>39.105598545074464</v>
+      </c>
+      <c r="D1287" s="4">
+        <v>39.026263392236501</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1288" s="1">
+        <v>46135.583333333336</v>
+      </c>
+      <c r="B1288" s="4">
+        <v>32.766080606344971</v>
+      </c>
+      <c r="C1288" s="4">
+        <v>39.229113878825359</v>
+      </c>
+      <c r="D1288" s="4">
+        <v>39.135933099972178</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1289" s="1">
+        <v>46135.625</v>
+      </c>
+      <c r="B1289" s="4">
+        <v>32.778187284745897</v>
+      </c>
+      <c r="C1289" s="4">
+        <v>39.224439888908755</v>
+      </c>
+      <c r="D1289" s="4">
+        <v>39.166019609994507</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1290" s="1">
+        <v>46135.666666666664</v>
+      </c>
+      <c r="B1290" s="4">
+        <v>32.797612668830396</v>
+      </c>
+      <c r="C1290" s="4">
+        <v>39.258684635162354</v>
+      </c>
+      <c r="D1290" s="4">
+        <v>39.174862552574218</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1291" s="1">
+        <v>46135.708333333336</v>
+      </c>
+      <c r="B1291" s="4">
+        <v>32.762976982480005</v>
+      </c>
+      <c r="C1291" s="4">
+        <v>39.19497456550598</v>
+      </c>
+      <c r="D1291" s="4">
+        <v>39.126495939749319</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1292" s="1">
+        <v>46135.75</v>
+      </c>
+      <c r="B1292" s="4">
+        <v>32.698813560122538</v>
+      </c>
+      <c r="C1292" s="4">
+        <v>39.091015799840292</v>
+      </c>
+      <c r="D1292" s="4">
+        <v>38.991732311882025</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1293" s="1">
+        <v>46135.791666666664</v>
+      </c>
+      <c r="B1293" s="4">
+        <v>32.583242541419132</v>
+      </c>
+      <c r="C1293" s="4">
+        <v>38.92970816930135</v>
+      </c>
+      <c r="D1293" s="4">
+        <v>38.852053403537631</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1294" s="1">
+        <v>46135.833333333336</v>
+      </c>
+      <c r="B1294" s="4">
+        <v>32.489548616939118</v>
+      </c>
+      <c r="C1294" s="4">
+        <v>38.803098400257255</v>
+      </c>
+      <c r="D1294" s="4">
+        <v>38.737158514395283</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1295" s="1">
+        <v>46135.875</v>
+      </c>
+      <c r="B1295" s="4">
+        <v>32.42150028069814</v>
+      </c>
+      <c r="C1295" s="4">
+        <v>38.739536716319897</v>
+      </c>
+      <c r="D1295" s="4">
+        <v>38.629195783657799</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1296" s="1">
+        <v>46135.916666666664</v>
+      </c>
+      <c r="B1296" s="4">
+        <v>32.444750162760414</v>
+      </c>
+      <c r="C1296" s="4">
+        <v>38.716482206491321</v>
+      </c>
+      <c r="D1296" s="4">
+        <v>38.576520598861748</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1297" s="1">
+        <v>46135.958333333336</v>
+      </c>
+      <c r="B1297" s="4">
+        <v>32.455763785044354</v>
+      </c>
+      <c r="C1297" s="4">
+        <v>38.704820143870819</v>
+      </c>
+      <c r="D1297" s="4">
+        <v>38.584333914257371</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1298" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B1298" s="4">
+        <v>32.456735992431639</v>
+      </c>
+      <c r="C1298" s="4">
+        <v>38.690312703450523</v>
+      </c>
+      <c r="D1298" s="4">
+        <v>38.563490072545555</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1299" s="1">
+        <v>46136.041666666664</v>
+      </c>
+      <c r="B1299" s="4">
+        <v>32.433213683537076</v>
+      </c>
+      <c r="C1299" s="4">
+        <v>38.691128306918671</v>
+      </c>
+      <c r="D1299" s="4">
+        <v>38.566053519869726</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1300" s="1">
+        <v>46136.083333333336</v>
+      </c>
+      <c r="B1300" s="4">
+        <v>32.392611689794627</v>
+      </c>
+      <c r="C1300" s="4">
+        <v>38.664651563432479</v>
+      </c>
+      <c r="D1300" s="4">
+        <v>38.532619161208373</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1301" s="1">
+        <v>46136.125</v>
+      </c>
+      <c r="B1301" s="4">
+        <v>32.373537796422056</v>
+      </c>
+      <c r="C1301" s="4">
+        <v>38.613726951729539</v>
+      </c>
+      <c r="D1301" s="4">
+        <v>38.491447933556522</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1302" s="1">
+        <v>46136.166666666664</v>
+      </c>
+      <c r="B1302" s="4">
+        <v>32.345610740101129</v>
+      </c>
+      <c r="C1302" s="4">
+        <v>38.60184604123107</v>
+      </c>
+      <c r="D1302" s="4">
+        <v>38.479315510024804</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1303" s="1">
+        <v>46136.208333333336</v>
+      </c>
+      <c r="B1303" s="4">
+        <v>32.325651903947197</v>
+      </c>
+      <c r="C1303" s="4">
+        <v>38.58031284014384</v>
+      </c>
+      <c r="D1303" s="4">
+        <v>38.478389002253437</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1304" s="1">
+        <v>46136.25</v>
+      </c>
+      <c r="B1304" s="4">
+        <v>32.26659708023071</v>
+      </c>
+      <c r="C1304" s="4">
+        <v>38.551145792007446</v>
+      </c>
+      <c r="D1304" s="4">
+        <v>38.459873084935403</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1305" s="1">
+        <v>46136.291666666664</v>
+      </c>
+      <c r="B1305" s="4">
+        <v>32.303184756778535</v>
+      </c>
+      <c r="C1305" s="4">
+        <v>38.582833086649579</v>
+      </c>
+      <c r="D1305" s="4">
+        <v>38.478702795578755</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1306" s="1">
+        <v>46136.333333333336</v>
+      </c>
+      <c r="B1306" s="4">
+        <v>32.34343220251926</v>
+      </c>
+      <c r="C1306" s="4">
+        <v>38.682145258585614</v>
+      </c>
+      <c r="D1306" s="4">
+        <v>38.563270259698655</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1307" s="1">
+        <v>46136.375</v>
+      </c>
+      <c r="B1307" s="4">
+        <v>32.364859488125504</v>
+      </c>
+      <c r="C1307" s="4">
+        <v>38.684618740990047</v>
+      </c>
+      <c r="D1307" s="4">
+        <v>38.584112586997165</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1308" s="1">
+        <v>46136.416666666664</v>
+      </c>
+      <c r="B1308" s="4">
+        <v>32.364774598439539</v>
+      </c>
+      <c r="C1308" s="4">
+        <v>38.727823116665789</v>
+      </c>
+      <c r="D1308" s="4">
+        <v>38.659824707410628</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1309" s="1">
+        <v>46136.458333333336</v>
+      </c>
+      <c r="B1309" s="4">
+        <v>32.441681251071749</v>
+      </c>
+      <c r="C1309" s="4">
+        <v>38.845468751589458</v>
+      </c>
+      <c r="D1309" s="4">
+        <v>38.75390890829091</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1310" s="1">
+        <v>46136.5</v>
+      </c>
+      <c r="B1310" s="4">
+        <v>32.480887833095736</v>
+      </c>
+      <c r="C1310" s="4">
+        <v>38.902022777663333</v>
+      </c>
+      <c r="D1310" s="4">
+        <v>38.808305532258927</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1311" s="1">
+        <v>46136.541666666664</v>
+      </c>
+      <c r="B1311" s="4">
+        <v>32.517222245534263</v>
+      </c>
+      <c r="C1311" s="4">
+        <v>38.943750529819063</v>
+      </c>
+      <c r="D1311" s="4">
+        <v>38.871606041253166</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1312" s="1">
+        <v>46136.583333333336</v>
+      </c>
+      <c r="B1312" s="4">
+        <v>32.556459172566733</v>
+      </c>
+      <c r="C1312" s="4">
+        <v>38.988541041480168</v>
+      </c>
+      <c r="D1312" s="4">
+        <v>38.926761917789278</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1313" s="1">
+        <v>46136.625</v>
+      </c>
+      <c r="B1313" s="4">
+        <v>32.661249764760335</v>
+      </c>
+      <c r="C1313" s="4">
+        <v>39.094045056237114</v>
+      </c>
+      <c r="D1313" s="4">
+        <v>38.979324242220045</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1314" s="1">
+        <v>46136.666666666664</v>
+      </c>
+      <c r="B1314" s="4">
+        <v>32.688410632992969</v>
+      </c>
+      <c r="C1314" s="4">
+        <v>39.130876557032266</v>
+      </c>
+      <c r="D1314" s="4">
+        <v>39.041077242457341</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1315" s="1">
+        <v>46136.708333333336</v>
+      </c>
+      <c r="B1315" s="4">
+        <v>32.688151708061312</v>
+      </c>
+      <c r="C1315" s="4">
+        <v>39.107119412952002</v>
+      </c>
+      <c r="D1315" s="4">
+        <v>38.998140633133538</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1316" s="1">
+        <v>46136.75</v>
+      </c>
+      <c r="B1316" s="4">
+        <v>32.628646278381346</v>
+      </c>
+      <c r="C1316" s="4">
+        <v>39.023686943054201</v>
+      </c>
+      <c r="D1316" s="4">
+        <v>38.94866457842059</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1317" s="1">
+        <v>46136.791666666664</v>
+      </c>
+      <c r="B1317" s="4">
+        <v>32.545602286303485</v>
+      </c>
+      <c r="C1317" s="4">
+        <v>38.907378016577823</v>
+      </c>
+      <c r="D1317" s="4">
+        <v>38.839588084169733</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1318" s="1">
+        <v>46136.833333333336</v>
+      </c>
+      <c r="B1318" s="4">
+        <v>32.496898432131168</v>
+      </c>
+      <c r="C1318" s="4">
+        <v>38.82263914744059</v>
+      </c>
+      <c r="D1318" s="4">
+        <v>38.755562256662934</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1319" s="1">
+        <v>46136.875</v>
+      </c>
+      <c r="B1319" s="4">
+        <v>32.471608566354824</v>
+      </c>
+      <c r="C1319" s="4">
+        <v>38.77723585340712</v>
+      </c>
+      <c r="D1319" s="4">
+        <v>38.690276181887917</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1320" s="1">
+        <v>46136.916666666664</v>
+      </c>
+      <c r="B1320" s="4">
+        <v>32.46859881966202</v>
+      </c>
+      <c r="C1320" s="4">
+        <v>38.757578180101184</v>
+      </c>
+      <c r="D1320" s="4">
+        <v>38.650013079333498</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1321" s="1">
+        <v>46136.958333333336</v>
+      </c>
+      <c r="B1321" s="4">
+        <v>32.452291488647461</v>
+      </c>
+      <c r="C1321" s="4">
+        <v>38.724505011240645</v>
+      </c>
+      <c r="D1321" s="4">
+        <v>38.612720534773473</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1322" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B1322" s="4">
+        <v>32.404133857193813</v>
+      </c>
+      <c r="C1322" s="4">
+        <v>38.648666292826334</v>
+      </c>
+      <c r="D1322" s="4">
+        <v>38.572808929555094</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1323" s="1">
+        <v>46137.041666666664</v>
+      </c>
+      <c r="B1323" s="4">
+        <v>32.347814590655624</v>
+      </c>
+      <c r="C1323" s="4">
+        <v>38.595013022422791</v>
+      </c>
+      <c r="D1323" s="4">
+        <v>38.527325346053878</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1324" s="1">
+        <v>46137.083333333336</v>
+      </c>
+      <c r="B1324" s="4">
+        <v>32.364772621963333</v>
+      </c>
+      <c r="C1324" s="4">
+        <v>38.61835334364573</v>
+      </c>
+      <c r="D1324" s="4">
+        <v>38.497236819055829</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1325" s="1">
+        <v>46137.125</v>
+      </c>
+      <c r="B1325" s="4">
+        <v>32.40657388130824</v>
+      </c>
+      <c r="C1325" s="4">
+        <v>38.672206035614018</v>
+      </c>
+      <c r="D1325" s="4">
+        <v>38.522815208668533</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1326" s="1">
+        <v>46137.166666666664</v>
+      </c>
+      <c r="B1326" s="4">
+        <v>32.477280432383218</v>
+      </c>
+      <c r="C1326" s="4">
+        <v>38.750155512491865</v>
+      </c>
+      <c r="D1326" s="4">
+        <v>38.594983283595568</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1327" s="1">
+        <v>46137.208333333336</v>
+      </c>
+      <c r="B1327" s="4">
+        <v>32.512135092417402</v>
+      </c>
+      <c r="C1327" s="4">
+        <v>38.789843877156578</v>
+      </c>
+      <c r="D1327" s="4">
+        <v>38.655437364378315</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1328" s="1">
+        <v>46137.25</v>
+      </c>
+      <c r="B1328" s="4">
+        <v>32.533958403269452</v>
+      </c>
+      <c r="C1328" s="4">
+        <v>38.814254302309273</v>
+      </c>
+      <c r="D1328" s="4">
+        <v>38.671149939046416</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1329" s="1">
+        <v>46137.291666666664</v>
+      </c>
+      <c r="B1329" s="4">
+        <v>32.499549527486167</v>
+      </c>
+      <c r="C1329" s="4">
+        <v>38.800751868360919</v>
+      </c>
+      <c r="D1329" s="4">
+        <v>38.70279500835435</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1330" s="1">
+        <v>46137.333333333336</v>
+      </c>
+      <c r="B1330" s="4">
+        <v>32.468366579691569</v>
+      </c>
+      <c r="C1330" s="4">
+        <v>38.791484663883843</v>
+      </c>
+      <c r="D1330" s="4">
+        <v>38.712131007830152</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1331" s="1">
+        <v>46137.375</v>
+      </c>
+      <c r="B1331" s="4">
+        <v>32.488021071751909</v>
+      </c>
+      <c r="C1331" s="4">
+        <v>38.795018990834556</v>
+      </c>
+      <c r="D1331" s="4">
+        <v>38.727437191615572</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1332" s="1">
+        <v>46137.416666666664</v>
+      </c>
+      <c r="B1332" s="4">
+        <v>32.503229681650801</v>
+      </c>
+      <c r="C1332" s="4">
+        <v>38.850119506439135</v>
+      </c>
+      <c r="D1332" s="4">
+        <v>38.752108672584598</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1333" s="1">
+        <v>46137.458333333336</v>
+      </c>
+      <c r="B1333" s="4">
+        <v>32.521333409945171</v>
+      </c>
+      <c r="C1333" s="4">
+        <v>38.891979061311588</v>
+      </c>
+      <c r="D1333" s="4">
+        <v>38.802625671903648</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1334" s="1">
+        <v>46137.5</v>
+      </c>
+      <c r="B1334" s="4">
+        <v>32.529948250452676</v>
+      </c>
+      <c r="C1334" s="4">
+        <v>38.932261043124726</v>
+      </c>
+      <c r="D1334" s="4">
+        <v>38.865637481885585</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1335" s="1">
+        <v>46137.541666666664</v>
+      </c>
+      <c r="B1335" s="4">
+        <v>32.627362049950491</v>
+      </c>
+      <c r="C1335" s="4">
+        <v>39.043546803792317</v>
+      </c>
+      <c r="D1335" s="4">
+        <v>38.935522194106142</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1336" s="1">
+        <v>46137.583333333336</v>
+      </c>
+      <c r="B1336" s="4">
+        <v>32.700138484107121</v>
+      </c>
+      <c r="C1336" s="4">
+        <v>39.146241458948111</v>
+      </c>
+      <c r="D1336" s="4">
+        <v>39.055267727563262</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1337" s="1">
+        <v>46137.625</v>
+      </c>
+      <c r="B1337" s="4">
+        <v>32.820208803812662</v>
+      </c>
+      <c r="C1337" s="4">
+        <v>39.274200518234913</v>
+      </c>
+      <c r="D1337" s="4">
+        <v>39.185776400606869</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1338" s="1">
+        <v>46137.666666666664</v>
+      </c>
+      <c r="B1338" s="4">
+        <v>32.932227934323819</v>
+      </c>
+      <c r="C1338" s="4">
+        <v>39.382938181559247</v>
+      </c>
+      <c r="D1338" s="4">
+        <v>39.285227293256142</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1339" s="1">
+        <v>46137.708333333336</v>
+      </c>
+      <c r="B1339" s="4">
+        <v>32.986832349876522</v>
+      </c>
+      <c r="C1339" s="4">
+        <v>39.419614919026692</v>
+      </c>
+      <c r="D1339" s="4">
+        <v>39.306849710952562</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1340" s="1">
+        <v>46137.75</v>
+      </c>
+      <c r="B1340" s="4">
+        <v>33.027430321471861</v>
+      </c>
+      <c r="C1340" s="4">
+        <v>39.470468470255533</v>
+      </c>
+      <c r="D1340" s="4">
+        <v>39.360958275548839</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1341" s="1">
+        <v>46137.791666666664</v>
+      </c>
+      <c r="B1341" s="4">
+        <v>32.989032872517903</v>
+      </c>
+      <c r="C1341" s="4">
+        <v>39.391353918711346</v>
+      </c>
+      <c r="D1341" s="4">
+        <v>39.28997341863586</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1342" s="1">
+        <v>46137.833333333336</v>
+      </c>
+      <c r="B1342" s="4">
+        <v>32.880321873300439</v>
+      </c>
+      <c r="C1342" s="4">
+        <v>39.250365136464438</v>
+      </c>
+      <c r="D1342" s="4">
+        <v>39.159996177885269</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1343" s="1">
+        <v>46137.875</v>
+      </c>
+      <c r="B1343" s="4">
+        <v>32.818997655621608</v>
+      </c>
+      <c r="C1343" s="4">
+        <v>39.175044184464674</v>
+      </c>
+      <c r="D1343" s="4">
+        <v>39.059393317043671</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1344" s="1">
+        <v>46137.916666666664</v>
+      </c>
+      <c r="B1344" s="4">
+        <v>32.736098250364648</v>
+      </c>
+      <c r="C1344" s="4">
+        <v>39.055424851637625</v>
+      </c>
+      <c r="D1344" s="4">
+        <v>38.971722309073968</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1345" s="1">
+        <v>46137.958333333336</v>
+      </c>
+      <c r="B1345" s="4">
+        <v>32.667682154973349</v>
+      </c>
+      <c r="C1345" s="4">
+        <v>38.978703218517879</v>
+      </c>
+      <c r="D1345" s="4">
+        <v>38.887565970189549</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1346" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B1346" s="4">
+        <v>32.644504181543986</v>
+      </c>
+      <c r="C1346" s="4">
+        <v>38.932148000447441</v>
+      </c>
+      <c r="D1346" s="4">
+        <v>38.65242845155818</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1347" s="1">
+        <v>46138.041666666664</v>
+      </c>
+      <c r="B1347" s="4">
+        <v>32.590000216166182</v>
+      </c>
+      <c r="C1347" s="4">
+        <v>38.865242804421321</v>
+      </c>
+      <c r="D1347" s="4">
+        <v>38.583327370486913</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1348" s="1">
+        <v>46138.083333333336</v>
+      </c>
+      <c r="B1348" s="4">
+        <v>32.597687584559125</v>
+      </c>
+      <c r="C1348" s="4">
+        <v>38.848794569287975</v>
+      </c>
+      <c r="D1348" s="4">
+        <v>38.543110593321551</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1349" s="1">
+        <v>46138.125</v>
+      </c>
+      <c r="B1349" s="4">
+        <v>32.498041655222572</v>
+      </c>
+      <c r="C1349" s="4">
+        <v>38.74844490914117</v>
+      </c>
+      <c r="D1349" s="4">
+        <v>38.474297529436328</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1350" s="1">
+        <v>46138.166666666664</v>
+      </c>
+      <c r="B1350" s="4">
+        <v>32.399874018334053</v>
+      </c>
+      <c r="C1350" s="4">
+        <v>38.65820282300313</v>
+      </c>
+      <c r="D1350" s="4">
+        <v>38.353358803283811</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1351" s="1">
+        <v>46138.208333333336</v>
+      </c>
+      <c r="B1351" s="4">
+        <v>32.320499155788347</v>
+      </c>
+      <c r="C1351" s="4">
+        <v>38.568619696299237</v>
+      </c>
+      <c r="D1351" s="4">
+        <v>38.275359680101595</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1352" s="1">
+        <v>46138.25</v>
+      </c>
+      <c r="B1352" s="4">
+        <v>32.249315320877805</v>
+      </c>
+      <c r="C1352" s="4">
+        <v>38.520781612396242</v>
+      </c>
+      <c r="D1352" s="4">
+        <v>38.217947956154731</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1353" s="1">
+        <v>46138.291666666664</v>
+      </c>
+      <c r="B1353" s="4">
+        <v>32.202915827433266</v>
+      </c>
+      <c r="C1353" s="4">
+        <v>38.35023493766785</v>
+      </c>
+      <c r="D1353" s="4">
+        <v>38.221671449881057</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1354" s="1">
+        <v>46138.333333333336</v>
+      </c>
+      <c r="B1354" s="4">
+        <v>32.213332430521646</v>
+      </c>
+      <c r="C1354" s="4">
+        <v>36.8780472808414</v>
+      </c>
+      <c r="D1354" s="4">
+        <v>36.808894149318313</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1355" s="1">
+        <v>46138.375</v>
+      </c>
+      <c r="B1355" s="4">
+        <v>32.31198993880173</v>
+      </c>
+      <c r="C1355" s="4">
+        <v>37.102669257587856</v>
+      </c>
+      <c r="D1355" s="4">
+        <v>36.761045508133343</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1356" s="1">
+        <v>46138.416666666664</v>
+      </c>
+      <c r="B1356" s="4">
+        <v>32.432385639760689</v>
+      </c>
+      <c r="C1356" s="4">
+        <v>38.764310193061831</v>
+      </c>
+      <c r="D1356" s="4">
+        <v>38.302307158995134</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1357" s="1">
+        <v>46138.458333333336</v>
+      </c>
+      <c r="B1357" s="4">
+        <v>32.569321004895194</v>
+      </c>
+      <c r="C1357" s="4">
+        <v>38.904010264078778</v>
+      </c>
+      <c r="D1357" s="4">
+        <v>38.60112819799869</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1358" s="1">
+        <v>46138.5</v>
+      </c>
+      <c r="B1358" s="4">
+        <v>32.621703611134336</v>
+      </c>
+      <c r="C1358" s="4">
+        <v>39.012552160205267</v>
+      </c>
+      <c r="D1358" s="4">
+        <v>38.757099754662917</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1359" s="1">
+        <v>46138.541666666664</v>
+      </c>
+      <c r="B1359" s="4">
+        <v>32.621266592873468</v>
+      </c>
+      <c r="C1359" s="4">
+        <v>39.024458436872166</v>
+      </c>
+      <c r="D1359" s="4">
+        <v>38.788685390178991</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1360" s="1">
+        <v>46138.583333333336</v>
+      </c>
+      <c r="B1360" s="4">
+        <v>32.701874627007378</v>
+      </c>
+      <c r="C1360" s="4">
+        <v>39.09801190433825</v>
+      </c>
+      <c r="D1360" s="4">
+        <v>38.796818909503116</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1361" s="1">
+        <v>46138.625</v>
+      </c>
+      <c r="B1361" s="4">
+        <v>32.702499590979684</v>
+      </c>
+      <c r="C1361" s="4">
+        <v>39.124210299385922</v>
+      </c>
+      <c r="D1361" s="4">
+        <v>38.847486286693147</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1362" s="1">
+        <v>46138.666666666664</v>
+      </c>
+      <c r="B1362" s="4">
+        <v>32.764999103546145</v>
+      </c>
+      <c r="C1362" s="4">
+        <v>39.177274227142334</v>
+      </c>
+      <c r="D1362" s="4">
+        <v>38.937809583719257</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1363" s="1">
+        <v>46138.708333333336</v>
+      </c>
+      <c r="B1363" s="4">
+        <v>32.809219082196556</v>
+      </c>
+      <c r="C1363" s="4">
+        <v>39.238281011581421</v>
+      </c>
+      <c r="D1363" s="4">
+        <v>38.954725198857282</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1364" s="1">
+        <v>46138.75</v>
+      </c>
+      <c r="B1364" s="4">
+        <v>32.842968074480694</v>
+      </c>
+      <c r="C1364" s="4">
+        <v>39.288749519983931</v>
+      </c>
+      <c r="D1364" s="4">
+        <v>39.033921668151848</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1365" s="1">
+        <v>46138.791666666664</v>
+      </c>
+      <c r="B1365" s="4">
+        <v>32.876978905995685</v>
+      </c>
+      <c r="C1365" s="4">
+        <v>39.309947840372722</v>
+      </c>
+      <c r="D1365" s="4">
+        <v>39.05043965238508</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1366" s="1">
+        <v>46138.833333333336</v>
+      </c>
+      <c r="B1366" s="4">
+        <v>32.818284765879312</v>
+      </c>
+      <c r="C1366" s="4">
+        <v>39.23877951304118</v>
+      </c>
+      <c r="D1366" s="4">
+        <v>38.996158230349998</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1367" s="1">
+        <v>46138.875</v>
+      </c>
+      <c r="B1367" s="4">
+        <v>32.784148484689219</v>
+      </c>
+      <c r="C1367" s="4">
+        <v>39.175901935718677</v>
+      </c>
+      <c r="D1367" s="4">
+        <v>38.9176713862147</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1368" s="1">
+        <v>46138.916666666664</v>
+      </c>
+      <c r="B1368" s="4">
+        <v>32.807607971859298</v>
+      </c>
+      <c r="C1368" s="4">
+        <v>39.167635140595607</v>
+      </c>
+      <c r="D1368" s="4">
+        <v>38.873917803251921</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1369" s="1">
+        <v>46138.958333333336</v>
+      </c>
+      <c r="B1369" s="4">
+        <v>32.798921567743477</v>
+      </c>
+      <c r="C1369" s="4">
+        <v>39.125390275319418</v>
+      </c>
+      <c r="D1369" s="4">
+        <v>38.842532959591964</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1370" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B1370" s="4">
+        <v>32.767079933322201</v>
+      </c>
+      <c r="C1370" s="4">
+        <v>39.071917936536998</v>
+      </c>
+      <c r="D1370" s="4">
+        <v>38.815382257068777</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1371" s="1">
+        <v>46139.041666666664</v>
+      </c>
+      <c r="B1371" s="4">
+        <v>32.746740831431346</v>
+      </c>
+      <c r="C1371" s="4">
+        <v>39.038155906919449</v>
+      </c>
+      <c r="D1371" s="4">
+        <v>38.775672996649824</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1372" s="1">
+        <v>46139.083333333336</v>
+      </c>
+      <c r="B1372" s="4">
+        <v>32.710808262749325</v>
+      </c>
+      <c r="C1372" s="4">
+        <v>38.9900427034923</v>
+      </c>
+      <c r="D1372" s="4">
+        <v>38.712661165473307</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1373" s="1">
+        <v>46139.125</v>
+      </c>
+      <c r="B1373" s="4">
+        <v>32.625461775915959</v>
+      </c>
+      <c r="C1373" s="4">
+        <v>38.952035779423184</v>
+      </c>
+      <c r="D1373" s="4">
+        <v>38.678035219746867</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1374" s="1">
+        <v>46139.166666666664</v>
+      </c>
+      <c r="B1374" s="4">
+        <v>32.636474238123213</v>
+      </c>
+      <c r="C1374" s="4">
+        <v>39.013523786332875</v>
+      </c>
+      <c r="D1374" s="4">
+        <v>38.688785571204285</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1375" s="1">
+        <v>46139.208333333336</v>
+      </c>
+      <c r="B1375" s="4">
+        <v>32.590145297050476</v>
+      </c>
+      <c r="C1375" s="4">
+        <v>38.98009366989136</v>
+      </c>
+      <c r="D1375" s="4">
+        <v>38.679710675140633</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1376" s="1">
+        <v>46139.25</v>
+      </c>
+      <c r="B1376" s="4">
+        <v>32.568291602664523</v>
+      </c>
+      <c r="C1376" s="4">
+        <v>38.971476395924888</v>
+      </c>
+      <c r="D1376" s="4">
+        <v>38.666710664741274</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1377" s="1">
+        <v>46139.291666666664</v>
+      </c>
+      <c r="B1377" s="4">
+        <v>32.538959036933051</v>
+      </c>
+      <c r="C1377" s="4">
+        <v>38.877951558430986</v>
+      </c>
+      <c r="D1377" s="4">
+        <v>38.591893624942344</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1378" s="1">
+        <v>46139.333333333336</v>
+      </c>
+      <c r="B1378" s="4">
+        <v>32.548666750590009</v>
+      </c>
+      <c r="C1378" s="4">
+        <v>38.899970109122144</v>
+      </c>
+      <c r="D1378" s="4">
+        <v>38.589114646013236</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1379" s="1">
+        <v>46139.375</v>
+      </c>
+      <c r="B1379" s="4">
+        <v>32.573979196548464</v>
+      </c>
+      <c r="C1379" s="4">
+        <v>38.921019690377371</v>
+      </c>
+      <c r="D1379" s="4">
+        <v>38.651776625620727</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1380" s="1">
+        <v>46139.416666666664</v>
+      </c>
+      <c r="B1380" s="4">
+        <v>32.63027127901713</v>
+      </c>
+      <c r="C1380" s="4">
+        <v>38.962989565531416</v>
+      </c>
+      <c r="D1380" s="4">
+        <v>38.711043753003068</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1381" s="1">
+        <v>46139.458333333336</v>
+      </c>
+      <c r="B1381" s="4">
+        <v>32.673697360356648</v>
+      </c>
+      <c r="C1381" s="4">
+        <v>39.03038374900818</v>
+      </c>
+      <c r="D1381" s="4">
+        <v>38.765245102072939</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1382" s="1">
+        <v>46139.5</v>
+      </c>
+      <c r="B1382" s="4">
+        <v>32.712647153169684</v>
+      </c>
+      <c r="C1382" s="4">
+        <v>39.077355424563088</v>
+      </c>
+      <c r="D1382" s="4">
+        <v>38.804357343047968</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1383" s="1">
+        <v>46139.541666666664</v>
+      </c>
+      <c r="B1383" s="4">
+        <v>32.708654322991002</v>
+      </c>
+      <c r="C1383" s="4">
+        <v>39.091966610796305</v>
+      </c>
+      <c r="D1383" s="4">
+        <v>38.838246161580784</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1384" s="1">
+        <v>46139.583333333336</v>
+      </c>
+      <c r="B1384" s="4">
+        <v>32.769803037876038</v>
+      </c>
+      <c r="C1384" s="4">
+        <v>39.169982014450376</v>
+      </c>
+      <c r="D1384" s="4">
+        <v>38.918459803612315</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1385" s="1">
+        <v>46139.625</v>
+      </c>
+      <c r="B1385" s="4">
+        <v>32.812072953945254</v>
+      </c>
+      <c r="C1385" s="4">
+        <v>39.23656071980794</v>
+      </c>
+      <c r="D1385" s="4">
+        <v>38.972877943803717</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1386" s="1">
+        <v>46139.666666666664</v>
+      </c>
+      <c r="B1386" s="4">
+        <v>32.870624669392903</v>
+      </c>
+      <c r="C1386" s="4">
+        <v>39.272876829667531</v>
+      </c>
+      <c r="D1386" s="4">
+        <v>38.992437808161668</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1387" s="1">
+        <v>46139.708333333336</v>
+      </c>
+      <c r="B1387" s="4">
+        <v>32.82479267120361</v>
+      </c>
+      <c r="C1387" s="4">
+        <v>39.23454988364017</v>
+      </c>
+      <c r="D1387" s="4">
+        <v>38.959934758053222</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1388" s="1">
+        <v>46139.75</v>
+      </c>
+      <c r="B1388" s="4">
+        <v>32.79936014811198</v>
+      </c>
+      <c r="C1388" s="4">
+        <v>39.24195874043</v>
+      </c>
+      <c r="D1388" s="4">
+        <v>38.94781443261418</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1389" s="1">
+        <v>46139.791666666664</v>
+      </c>
+      <c r="B1389" s="4">
+        <v>32.750639756520592</v>
+      </c>
+      <c r="C1389" s="4">
+        <v>39.171009005033056</v>
+      </c>
+      <c r="D1389" s="4">
+        <v>38.894812495645034</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1390" s="1">
+        <v>46139.833333333336</v>
+      </c>
+      <c r="B1390" s="4">
+        <v>32.723395830790203</v>
+      </c>
+      <c r="C1390" s="4">
+        <v>39.14731790224711</v>
+      </c>
+      <c r="D1390" s="4">
+        <v>38.874760842380951</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1391" s="1">
+        <v>46139.875</v>
+      </c>
+      <c r="B1391" s="4">
+        <v>32.719207733472189</v>
+      </c>
+      <c r="C1391" s="4">
+        <v>39.116588163375852</v>
+      </c>
+      <c r="D1391" s="4">
+        <v>38.819125456646951</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1392" s="1">
+        <v>46139.916666666664</v>
+      </c>
+      <c r="B1392" s="4">
+        <v>32.72617988851335</v>
+      </c>
+      <c r="C1392" s="4">
+        <v>39.075165823734167</v>
+      </c>
+      <c r="D1392" s="4">
+        <v>38.780829861023697</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1393" s="1">
+        <v>46139.958333333336</v>
+      </c>
+      <c r="B1393" s="4">
+        <v>32.708922470940486</v>
+      </c>
+      <c r="C1393" s="4">
+        <v>39.042484985377257</v>
+      </c>
+      <c r="D1393" s="4">
+        <v>38.726303746813414</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1394" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B1394" s="4">
+        <v>32.710138161977135</v>
+      </c>
+      <c r="C1394" s="4">
+        <v>39.04583894588329</v>
+      </c>
+      <c r="D1394" s="4">
+        <v>38.76011682733148</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1395" s="1">
+        <v>46140.041666666664</v>
+      </c>
+      <c r="B1395" s="4">
+        <v>32.617846859825981</v>
+      </c>
+      <c r="C1395" s="4">
+        <v>38.923581067721052</v>
+      </c>
+      <c r="D1395" s="4">
+        <v>38.682098922585737</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1396" s="1">
+        <v>46140.083333333336</v>
+      </c>
+      <c r="B1396" s="4">
+        <v>32.553680335150823</v>
+      </c>
+      <c r="C1396" s="4">
+        <v>38.816296144326529</v>
+      </c>
+      <c r="D1396" s="4">
+        <v>38.576855722018188</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1397" s="1">
+        <v>46140.125</v>
+      </c>
+      <c r="B1397" s="4">
+        <v>32.465624226464165</v>
+      </c>
+      <c r="C1397" s="4">
+        <v>38.762233086427052</v>
+      </c>
+      <c r="D1397" s="4">
+        <v>38.503242594359065</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1398" s="1">
+        <v>46140.166666666664</v>
+      </c>
+      <c r="B1398" s="4">
+        <v>32.439165348476834</v>
+      </c>
+      <c r="C1398" s="4">
+        <v>38.751788128746881</v>
+      </c>
+      <c r="D1398" s="4">
+        <v>38.474117998390795</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1399" s="1">
+        <v>46140.208333333336</v>
+      </c>
+      <c r="B1399" s="4">
+        <v>32.459582551320395</v>
+      </c>
+      <c r="C1399" s="4">
+        <v>38.781550537215338</v>
+      </c>
+      <c r="D1399" s="4">
+        <v>38.484333779427331</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1400" s="1">
+        <v>46140.25</v>
+      </c>
+      <c r="B1400" s="4">
+        <v>32.512499618530271</v>
+      </c>
+      <c r="C1400" s="4">
+        <v>38.828146680196127</v>
+      </c>
+      <c r="D1400" s="4">
+        <v>38.53524064595566</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1401" s="1">
+        <v>46140.291666666664</v>
+      </c>
+      <c r="B1401" s="4">
+        <v>32.47187509536743</v>
+      </c>
+      <c r="C1401" s="4">
+        <v>38.825807499885556</v>
+      </c>
+      <c r="D1401" s="4">
+        <v>38.543446700589939</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1402" s="1">
+        <v>46140.333333333336</v>
+      </c>
+      <c r="B1402" s="4">
+        <v>32.457159495771975</v>
+      </c>
+      <c r="C1402" s="4">
+        <v>38.804759849442377</v>
+      </c>
+      <c r="D1402" s="4">
+        <v>38.536810126017073</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1403" s="1">
+        <v>46140.375</v>
+      </c>
+      <c r="B1403" s="4">
+        <v>32.484923354366366</v>
+      </c>
+      <c r="C1403" s="4">
+        <v>38.827407736248439</v>
+      </c>
+      <c r="D1403" s="4">
+        <v>38.579488800804484</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1404" s="1">
+        <v>46140.416666666664</v>
+      </c>
+      <c r="B1404" s="4">
+        <v>32.583264048894243</v>
+      </c>
+      <c r="C1404" s="4">
+        <v>38.925904814402266</v>
+      </c>
+      <c r="D1404" s="4">
+        <v>38.639539662533892</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1405" s="1">
+        <v>46140.458333333336</v>
+      </c>
+      <c r="B1405" s="4">
+        <v>32.618819125493367</v>
+      </c>
+      <c r="C1405" s="4">
+        <v>38.947404665417139</v>
+      </c>
+      <c r="D1405" s="4">
+        <v>38.673988519278282</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1406" s="1">
+        <v>46140.5</v>
+      </c>
+      <c r="B1406" s="4">
+        <v>32.708958435058591</v>
+      </c>
+      <c r="C1406" s="4">
+        <v>39.035104179382323</v>
+      </c>
+      <c r="D1406" s="4">
+        <v>38.768624752275691</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1407" s="1">
+        <v>46140.541666666664</v>
+      </c>
+      <c r="B1407" s="4">
+        <v>32.744791412353514</v>
+      </c>
+      <c r="C1407" s="4">
+        <v>39.078567987018161</v>
+      </c>
+      <c r="D1407" s="4">
+        <v>38.843960468893854</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1408" s="1">
+        <v>46140.583333333336</v>
+      </c>
+      <c r="B1408" s="4">
+        <v>32.816875553131105</v>
+      </c>
+      <c r="C1408" s="4">
+        <v>39.142438650131226</v>
+      </c>
+      <c r="D1408" s="4">
+        <v>38.89348109383338</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1409" s="1">
+        <v>46140.625</v>
+      </c>
+      <c r="B1409" s="4">
+        <v>32.901291853586834</v>
+      </c>
+      <c r="C1409" s="4">
+        <v>39.223072433471678</v>
+      </c>
+      <c r="D1409" s="4">
+        <v>38.940889064157254</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1410" s="1">
+        <v>46140.666666666664</v>
+      </c>
+      <c r="B1410" s="4">
+        <v>32.912666266759238</v>
+      </c>
+      <c r="C1410" s="4">
+        <v>39.257386563040995</v>
+      </c>
+      <c r="D1410" s="4">
+        <v>38.996858487598978</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1411" s="1">
+        <v>46140.708333333336</v>
+      </c>
+      <c r="B1411" s="4">
+        <v>32.8816667397817</v>
+      </c>
+      <c r="C1411" s="4">
+        <v>39.241645280416911</v>
+      </c>
+      <c r="D1411" s="4">
+        <v>38.970422816829405</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1412" s="1">
+        <v>46140.75</v>
+      </c>
+      <c r="B1412" s="4">
+        <v>32.864999580383298</v>
+      </c>
+      <c r="C1412" s="4">
+        <v>39.230029466038651</v>
+      </c>
+      <c r="D1412" s="4">
+        <v>38.926670317569524</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1413" s="1">
+        <v>46140.791666666664</v>
+      </c>
+      <c r="B1413" s="4">
+        <v>32.730944832747547</v>
+      </c>
+      <c r="C1413" s="4">
+        <v>39.099032113287187</v>
+      </c>
+      <c r="D1413" s="4">
+        <v>38.844328857735064</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1414" s="1">
+        <v>46140.833333333336</v>
+      </c>
+      <c r="B1414" s="4">
+        <v>32.58718052646978</v>
+      </c>
+      <c r="C1414" s="4">
+        <v>38.954307270050052</v>
+      </c>
+      <c r="D1414" s="4">
+        <v>38.694113489990052</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1415" s="1">
+        <v>46140.875</v>
+      </c>
+      <c r="B1415" s="4">
+        <v>32.601874876022336</v>
+      </c>
+      <c r="C1415" s="4">
+        <v>38.930358325110539</v>
+      </c>
+      <c r="D1415" s="4">
+        <v>38.616841492041495</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1416" s="1">
+        <v>46140.916666666664</v>
+      </c>
+      <c r="B1416" s="4">
+        <v>32.6665664990743</v>
+      </c>
+      <c r="C1416" s="4">
+        <v>39.001267507341176</v>
+      </c>
+      <c r="D1416" s="4">
+        <v>38.656526016387573</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1417" s="1">
+        <v>46140.958333333336</v>
+      </c>
+      <c r="B1417" s="4">
+        <v>32.612599690755211</v>
+      </c>
+      <c r="C1417" s="4">
+        <v>38.944956951671173</v>
+      </c>
+      <c r="D1417" s="4">
+        <v>38.676353412567451</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1418" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B1418" s="4">
+        <v>32.623489268620808</v>
+      </c>
+      <c r="C1418" s="4">
+        <v>38.908613072122847</v>
+      </c>
+      <c r="D1418" s="4">
+        <v>38.605458489130044</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1419" s="1">
+        <v>46141.041666666664</v>
+      </c>
+      <c r="B1419" s="4">
+        <v>32.586927207310993</v>
+      </c>
+      <c r="C1419" s="4">
+        <v>38.885684313092916</v>
+      </c>
+      <c r="D1419" s="4">
+        <v>38.580034054787966</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1420" s="1">
+        <v>46141.083333333336</v>
+      </c>
+      <c r="B1420" s="4">
+        <v>32.507083098093666</v>
+      </c>
+      <c r="C1420" s="4">
+        <v>38.81432362397512</v>
+      </c>
+      <c r="D1420" s="4">
+        <v>38.516277428320365</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1421" s="1">
+        <v>46141.125</v>
+      </c>
+      <c r="B1421" s="4">
+        <v>32.441459019978844</v>
+      </c>
+      <c r="C1421" s="4">
+        <v>38.757083639028288</v>
+      </c>
+      <c r="D1421" s="4">
+        <v>38.499067281753177</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1422" s="1">
+        <v>46141.166666666664</v>
+      </c>
+      <c r="B1422" s="4">
+        <v>32.448125330607098</v>
+      </c>
+      <c r="C1422" s="4">
+        <v>38.752247032600032</v>
+      </c>
+      <c r="D1422" s="4">
+        <v>38.466713354833225</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1423" s="1">
+        <v>46141.208333333336</v>
+      </c>
+      <c r="B1423" s="4">
+        <v>32.43979212443034</v>
+      </c>
+      <c r="C1423" s="4">
+        <v>38.763229382832847</v>
+      </c>
+      <c r="D1423" s="4">
+        <v>38.425180263647718</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1424" s="1">
+        <v>46141.25</v>
+      </c>
+      <c r="B1424" s="4">
+        <v>32.369280112873426</v>
+      </c>
+      <c r="C1424" s="4">
+        <v>38.704583059946692</v>
+      </c>
+      <c r="D1424" s="4">
+        <v>38.424213574787736</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1425" s="1">
+        <v>46141.291666666664</v>
+      </c>
+      <c r="B1425" s="4">
+        <v>32.365907881765651</v>
+      </c>
+      <c r="C1425" s="4">
+        <v>38.708697923024495</v>
+      </c>
+      <c r="D1425" s="4">
+        <v>38.442438668990619</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1426" s="1">
+        <v>46141.333333333336</v>
+      </c>
+      <c r="B1426" s="4">
+        <v>32.338562978108726</v>
+      </c>
+      <c r="C1426" s="4">
+        <v>38.718879286448164</v>
+      </c>
+      <c r="D1426" s="4">
+        <v>38.469396010784806</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1427" s="1">
+        <v>46141.375</v>
+      </c>
+      <c r="B1427" s="4">
+        <v>32.406597503026326</v>
+      </c>
+      <c r="C1427" s="4">
+        <v>38.767005411783856</v>
+      </c>
+      <c r="D1427" s="4">
+        <v>38.484020696195401</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1428" s="1">
+        <v>46141.416666666664</v>
+      </c>
+      <c r="B1428" s="4">
+        <v>32.450902287165327</v>
+      </c>
+      <c r="C1428" s="4">
+        <v>38.79342064327664</v>
+      </c>
+      <c r="D1428" s="4">
+        <v>38.503186409900529</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1429" s="1">
+        <v>46141.458333333336</v>
+      </c>
+      <c r="B1429" s="4">
+        <v>32.473750114440918</v>
+      </c>
+      <c r="C1429" s="4">
+        <v>38.813975927564833</v>
+      </c>
+      <c r="D1429" s="4">
+        <v>38.552968202184758</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1430" s="1">
+        <v>46141.5</v>
+      </c>
+      <c r="B1430" s="4">
+        <v>32.471652605268687</v>
+      </c>
+      <c r="C1430" s="4">
+        <v>38.805598513285318</v>
+      </c>
+      <c r="D1430" s="4">
+        <v>38.558671695166346</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1431" s="1">
+        <v>46141.541666666664</v>
+      </c>
+      <c r="B1431" s="4">
+        <v>32.480013622707794</v>
+      </c>
+      <c r="C1431" s="4">
+        <v>38.810822014581589</v>
+      </c>
+      <c r="D1431" s="4">
+        <v>38.524025009194602</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1432" s="1">
+        <v>46141.583333333336</v>
+      </c>
+      <c r="B1432" s="4">
+        <v>32.559167130788168</v>
+      </c>
+      <c r="C1432" s="4">
+        <v>38.844021501238387</v>
+      </c>
+      <c r="D1432" s="4">
+        <v>38.562116481211859</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1433" s="1">
+        <v>46141.625</v>
+      </c>
+      <c r="B1433" s="4">
+        <v>32.581500225067138</v>
+      </c>
+      <c r="C1433" s="4">
+        <v>38.85424529105898</v>
+      </c>
+      <c r="D1433" s="4">
+        <v>38.578435462823769</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1434" s="1">
+        <v>46141.666666666664</v>
+      </c>
+      <c r="B1434" s="4">
+        <v>32.63204155815972</v>
+      </c>
+      <c r="C1434" s="4">
+        <v>38.911579212309825</v>
+      </c>
+      <c r="D1434" s="4">
+        <v>38.627185354246031</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1435" s="1">
+        <v>46141.708333333336</v>
+      </c>
+      <c r="B1435" s="4">
+        <v>32.682916588253448</v>
+      </c>
+      <c r="C1435" s="4">
+        <v>38.985294606950546</v>
+      </c>
+      <c r="D1435" s="4">
+        <v>38.68466905057857</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1436" s="1">
+        <v>46141.75</v>
+      </c>
+      <c r="B1436" s="4">
+        <v>32.606874275207517</v>
+      </c>
+      <c r="C1436" s="4">
+        <v>38.967937266031903</v>
+      </c>
+      <c r="D1436" s="4">
+        <v>38.673194078637181</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1437" s="1">
+        <v>46141.791666666664</v>
+      </c>
+      <c r="B1437" s="4">
+        <v>32.564981006853507</v>
+      </c>
+      <c r="C1437" s="4">
+        <v>38.875604451497395</v>
+      </c>
+      <c r="D1437" s="4">
+        <v>38.610822158279099</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1438" s="1">
+        <v>46141.833333333336</v>
+      </c>
+      <c r="B1438" s="4">
+        <v>32.540795499628238</v>
+      </c>
+      <c r="C1438" s="4">
+        <v>38.850312945048017</v>
+      </c>
+      <c r="D1438" s="4">
+        <v>38.559659970838659</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1439" s="1">
+        <v>46141.875</v>
+      </c>
+      <c r="B1439" s="4">
+        <v>32.507348913134955</v>
+      </c>
+      <c r="C1439" s="4">
+        <v>38.826458314259845</v>
+      </c>
+      <c r="D1439" s="4">
+        <v>38.525497113265082</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1440" s="1">
+        <v>46141.916666666664</v>
+      </c>
+      <c r="B1440" s="4">
+        <v>32.450833479563393</v>
+      </c>
+      <c r="C1440" s="4">
+        <v>38.768854554494219</v>
+      </c>
+      <c r="D1440" s="4">
+        <v>38.46887694121672</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1441" s="1">
+        <v>46141.958333333336</v>
+      </c>
+      <c r="B1441" s="4">
+        <v>32.391874631245933</v>
+      </c>
+      <c r="C1441" s="4">
+        <v>38.69072910944621</v>
+      </c>
+      <c r="D1441" s="4">
+        <v>38.3981926383169</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1442" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B1442" s="4">
+        <v>32.35187524159749</v>
+      </c>
+      <c r="C1442" s="4">
+        <v>38.647679747067968</v>
+      </c>
+      <c r="D1442" s="4">
+        <v>38.322291891321463</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1443" s="1">
+        <v>46142.041666666664</v>
+      </c>
+      <c r="B1443" s="4">
+        <v>32.345833365122481</v>
+      </c>
+      <c r="C1443" s="4">
+        <v>38.619923745668849</v>
+      </c>
+      <c r="D1443" s="4">
+        <v>38.314467904727657</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1444" s="1">
+        <v>46142.083333333336</v>
+      </c>
+      <c r="B1444" s="4">
+        <v>32.294375292460124</v>
+      </c>
+      <c r="C1444" s="4">
+        <v>38.598567173216075</v>
+      </c>
+      <c r="D1444" s="4">
+        <v>38.290861820066588</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1445" s="1">
+        <v>46142.125</v>
+      </c>
+      <c r="B1445" s="4">
+        <v>32.281875578562421</v>
+      </c>
+      <c r="C1445" s="4">
+        <v>38.589453087912666</v>
+      </c>
+      <c r="D1445" s="4">
+        <v>38.287243732991264</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1446" s="1">
+        <v>46142.166666666664</v>
+      </c>
+      <c r="B1446" s="4">
+        <v>32.284028021494549</v>
+      </c>
+      <c r="C1446" s="4">
+        <v>38.616338852473667</v>
+      </c>
+      <c r="D1446" s="4">
+        <v>38.291586493181981</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1447" s="1">
+        <v>46142.208333333336</v>
+      </c>
+      <c r="B1447" s="4">
+        <v>32.32493050893148</v>
+      </c>
+      <c r="C1447" s="4">
+        <v>38.66169923600696</v>
+      </c>
+      <c r="D1447" s="4">
+        <v>38.338874034683272</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1448" s="1">
+        <v>46142.25</v>
+      </c>
+      <c r="B1448" s="4">
+        <v>32.316458193461102</v>
+      </c>
+      <c r="C1448" s="4">
+        <v>38.674721813201906</v>
+      </c>
+      <c r="D1448" s="4">
+        <v>38.353418028767798</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1449" s="1">
+        <v>46142.291666666664</v>
+      </c>
+      <c r="B1449" s="4">
+        <v>32.316682595473068</v>
+      </c>
+      <c r="C1449" s="4">
+        <v>38.70731091101964</v>
+      </c>
+      <c r="D1449" s="4">
+        <v>38.392341989314367</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1450" s="1">
+        <v>46142.333333333336</v>
+      </c>
+      <c r="B1450" s="4">
+        <v>32.356599685945227</v>
+      </c>
+      <c r="C1450" s="4">
+        <v>38.737792988618217</v>
+      </c>
+      <c r="D1450" s="4">
+        <v>38.417523656762377</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1451" s="1">
+        <v>46142.375</v>
+      </c>
+      <c r="B1451" s="4">
+        <v>32.370233233909161</v>
+      </c>
+      <c r="C1451" s="4">
+        <v>38.756142699718474</v>
+      </c>
+      <c r="D1451" s="4">
+        <v>38.456219614549731</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1452" s="1">
+        <v>46142.416666666664</v>
+      </c>
+      <c r="B1452" s="4">
+        <v>32.370666198852732</v>
+      </c>
+      <c r="C1452" s="4">
+        <v>38.744430426756544</v>
+      </c>
+      <c r="D1452" s="4">
+        <v>38.486949156379481</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1453" s="1">
+        <v>46142.458333333336</v>
+      </c>
+      <c r="B1453" s="4">
+        <v>32.399176950332446</v>
+      </c>
+      <c r="C1453" s="4">
+        <v>38.769195806412469</v>
+      </c>
+      <c r="D1453" s="4">
+        <v>38.50168783722804</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1454" s="1">
+        <v>46142.5</v>
+      </c>
+      <c r="B1454" s="4">
+        <v>32.454008166717763</v>
+      </c>
+      <c r="C1454" s="4">
+        <v>38.786159456343874</v>
+      </c>
+      <c r="D1454" s="4">
+        <v>38.533016049610715</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1455" s="1">
+        <v>46142.541666666664</v>
+      </c>
+      <c r="B1455" s="4">
+        <v>32.527841273221107</v>
+      </c>
+      <c r="C1455" s="4">
+        <v>38.816883913675944</v>
+      </c>
+      <c r="D1455" s="4">
+        <v>38.57772500831755</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1456" s="1">
+        <v>46142.583333333336</v>
+      </c>
+      <c r="B1456" s="4">
+        <v>32.641770513852435</v>
+      </c>
+      <c r="C1456" s="4">
+        <v>38.930937655766805</v>
+      </c>
+      <c r="D1456" s="4">
+        <v>38.64908461623471</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1457" s="1">
+        <v>46142.625</v>
+      </c>
+      <c r="B1457" s="4">
+        <v>32.770990705490114</v>
+      </c>
+      <c r="C1457" s="4">
+        <v>39.047865247726442</v>
+      </c>
+      <c r="D1457" s="4">
+        <v>38.76211882543641</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1458" s="1">
+        <v>46142.666666666664</v>
+      </c>
+      <c r="B1458" s="4">
+        <v>32.849531674385069</v>
+      </c>
+      <c r="C1458" s="4">
+        <v>39.122499783833824</v>
+      </c>
+      <c r="D1458" s="4">
+        <v>38.837710793092072</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1459" s="1">
+        <v>46142.708333333336</v>
+      </c>
+      <c r="B1459" s="4">
+        <v>32.913880264759065</v>
+      </c>
+      <c r="C1459" s="4">
+        <v>39.173418812692901</v>
+      </c>
+      <c r="D1459" s="4">
+        <v>38.913785857787907</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1460" s="1">
+        <v>46142.75</v>
+      </c>
+      <c r="B1460" s="4">
+        <v>32.887369398276014</v>
+      </c>
+      <c r="C1460" s="4">
+        <v>39.203924810150525</v>
+      </c>
+      <c r="D1460" s="4">
+        <v>38.910026824135265</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1461" s="1">
+        <v>46142.791666666664</v>
+      </c>
+      <c r="B1461" s="4">
+        <v>32.884113454818724</v>
+      </c>
+      <c r="C1461" s="4">
+        <v>39.177447848849823</v>
+      </c>
+      <c r="D1461" s="4">
+        <v>38.880405691197886</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1462" s="1">
+        <v>46142.833333333336</v>
+      </c>
+      <c r="B1462" s="4">
+        <v>32.811302264531456</v>
+      </c>
+      <c r="C1462" s="4">
+        <v>39.131087134944067</v>
+      </c>
+      <c r="D1462" s="4">
+        <v>38.837247133762695</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1463" s="1">
+        <v>46142.875</v>
+      </c>
+      <c r="B1463" s="4">
+        <v>32.66086795594957</v>
+      </c>
+      <c r="C1463" s="4">
+        <v>38.966568807760872</v>
+      </c>
+      <c r="D1463" s="4">
+        <v>38.701180603358232</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1464" s="1">
+        <v>46142.916666666664</v>
+      </c>
+      <c r="B1464" s="4">
+        <v>32.637530145074571</v>
+      </c>
+      <c r="C1464" s="4">
+        <v>38.953913510640461</v>
+      </c>
+      <c r="D1464" s="4">
+        <v>38.651571168112085</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1465" s="1">
+        <v>46142.958333333336</v>
+      </c>
+      <c r="B1465" s="4">
+        <v>32.633754844882887</v>
+      </c>
+      <c r="C1465" s="4">
+        <v>38.968207846554847</v>
+      </c>
+      <c r="D1465" s="4">
+        <v>38.657021682517978</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1466" s="1"/>
+      <c r="B1466" s="4"/>
+      <c r="C1466" s="4"/>
+      <c r="D1466" s="4"/>
+    </row>
+    <row r="1467" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1467" s="1"/>
+      <c r="B1467" s="4"/>
+      <c r="C1467" s="4"/>
+      <c r="D1467" s="4"/>
+    </row>
+    <row r="1468" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1468" s="1"/>
+      <c r="B1468" s="4"/>
+      <c r="C1468" s="4"/>
+      <c r="D1468" s="4"/>
+    </row>
+    <row r="1469" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1469" s="1"/>
+      <c r="B1469" s="4"/>
+      <c r="C1469" s="4"/>
+      <c r="D1469" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
